--- a/Full-LC-AUTO/data inputs/Variants-excel_jean.xlsx
+++ b/Full-LC-AUTO/data inputs/Variants-excel_jean.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work-mom\Code-Tools\Full-LC-AUTO\data inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESHAAN\HAKUR\work--fk-tools\Full-LC-AUTO\data inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A13D3C4-62F6-4B78-8ED9-E18CAA097C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{012F2C9F-D585-40F7-A0C4-ECAE4ABBF8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="21">
   <si>
     <t>kind</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>Beige</t>
+  </si>
+  <si>
+    <t>size_variant_4</t>
   </si>
 </sst>
 </file>
@@ -420,13 +423,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -445,8 +448,11 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -457,16 +463,19 @@
         <v>7</v>
       </c>
       <c r="D2">
+        <v>26</v>
+      </c>
+      <c r="E2">
         <v>30</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>32</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -477,16 +486,19 @@
         <v>7</v>
       </c>
       <c r="D3">
+        <v>26</v>
+      </c>
+      <c r="E3">
         <v>30</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>32</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -497,16 +509,19 @@
         <v>7</v>
       </c>
       <c r="D4">
+        <v>26</v>
+      </c>
+      <c r="E4">
         <v>30</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>32</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -517,13 +532,16 @@
         <v>7</v>
       </c>
       <c r="D5">
+        <v>26</v>
+      </c>
+      <c r="E5">
         <v>30</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -534,9 +552,12 @@
         <v>7</v>
       </c>
       <c r="D6">
+        <v>26</v>
+      </c>
+      <c r="E6">
         <v>30</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>32</v>
       </c>
     </row>
